--- a/fig_tables.xlsx
+++ b/fig_tables.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/zoekao/Documents/HCAHPS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4DA08AF-4BC8-7146-ABD9-1D3A8B1CE797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A26F2F60-58A7-D94A-AF1A-F537A9675A23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20" yWindow="680" windowWidth="34540" windowHeight="20480" xr2:uid="{8934C100-C541-4414-89AB-449DE59BDFC5}"/>
+    <workbookView xWindow="20" yWindow="680" windowWidth="34540" windowHeight="20480" activeTab="2" xr2:uid="{8934C100-C541-4414-89AB-449DE59BDFC5}"/>
   </bookViews>
   <sheets>
     <sheet name="fig1" sheetId="1" r:id="rId1"/>
@@ -688,7 +688,7 @@
       <name val="Roboto"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -698,6 +698,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -720,11 +726,12 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -768,14 +775,28 @@
     <xf numFmtId="49" fontId="2" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="0" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="2">
+  <cellStyles count="3">
     <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1299,7 +1320,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="18" spans="18:18" ht="17" x14ac:dyDescent="0.2">
-      <c r="R18" s="22"/>
+      <c r="R18" s="21"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1309,13 +1330,14 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A730F9CC-C942-4C53-AF4F-6809A5E39D2A}">
-  <dimension ref="A1:N49"/>
+  <dimension ref="A1:P49"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="44.1640625" customWidth="1"/>
     <col min="2" max="5" width="11.83203125" customWidth="1"/>
     <col min="6" max="6" width="14.5" bestFit="1" customWidth="1"/>
     <col min="7" max="15" width="0" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="16.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.2">
@@ -1555,7 +1577,7 @@
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
     </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>17</v>
       </c>
@@ -1596,7 +1618,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -1637,7 +1659,7 @@
         <v>0.89847259999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>19</v>
       </c>
@@ -1678,8 +1700,8 @@
         <v>37.5</v>
       </c>
     </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A20" t="s">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A20" s="23" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="8">
@@ -1718,9 +1740,13 @@
       <c r="N20" s="10">
         <v>10100000</v>
       </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A21" t="s">
+      <c r="P20" s="31">
+        <f>(B20-D20)/D20</f>
+        <v>2.4458995039320506E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A21" s="23" t="s">
         <v>21</v>
       </c>
       <c r="B21" s="7">
@@ -1763,9 +1789,13 @@
       <c r="N21" s="9">
         <v>0.3829573</v>
       </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A22" t="s">
+      <c r="P21" s="24">
+        <f>(B21-D21)</f>
+        <v>2.4470599999999969</v>
+      </c>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A22" s="23" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="7">
@@ -1808,54 +1838,62 @@
       <c r="N22" s="9">
         <v>0.99059779999999997</v>
       </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A23" t="s">
+      <c r="P22" s="24">
+        <f t="shared" ref="P22:P29" si="2">(B22-D22)</f>
+        <v>-10.685850000000002</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16" s="25" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B23" s="7">
+      <c r="B23" s="26">
         <f t="shared" si="1"/>
         <v>11.236790000000001</v>
       </c>
-      <c r="C23" s="7">
+      <c r="C23" s="26">
         <f t="shared" si="1"/>
         <v>12.621129999999999</v>
       </c>
-      <c r="D23" s="7">
+      <c r="D23" s="26">
         <f t="shared" si="0"/>
         <v>11.54082</v>
       </c>
-      <c r="E23" s="7">
+      <c r="E23" s="26">
         <f t="shared" si="0"/>
         <v>13.06776</v>
       </c>
-      <c r="G23" s="9">
+      <c r="G23" s="27">
         <v>0.11236790000000001</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="27">
         <v>0.1262113</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="27">
         <v>0</v>
       </c>
-      <c r="J23" s="9">
+      <c r="J23" s="27">
         <v>0.82866439999999997</v>
       </c>
-      <c r="K23" s="9">
+      <c r="K23" s="27">
         <v>0.1154082</v>
       </c>
-      <c r="L23" s="9">
+      <c r="L23" s="27">
         <v>0.1306776</v>
       </c>
-      <c r="M23" s="9">
+      <c r="M23" s="27">
         <v>0</v>
       </c>
-      <c r="N23" s="9">
+      <c r="N23" s="27">
         <v>0.86399570000000003</v>
       </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A24" t="s">
+      <c r="P23" s="28">
+        <f t="shared" si="2"/>
+        <v>-0.30402999999999913</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A24" s="23" t="s">
         <v>24</v>
       </c>
       <c r="B24" s="7">
@@ -1898,8 +1936,12 @@
       <c r="N24" s="9">
         <v>0.53212930000000003</v>
       </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="P24" s="24">
+        <f>(B24-D24)</f>
+        <v>2.4866399999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>25</v>
       </c>
@@ -1943,9 +1985,13 @@
       <c r="N25" s="9">
         <v>0.52944539999999995</v>
       </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="P25" s="30">
+        <f>(B25-D25)/D25</f>
+        <v>5.7117997871273953E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A26" s="23" t="s">
         <v>26</v>
       </c>
       <c r="B26" s="7">
@@ -1988,9 +2034,13 @@
       <c r="N26" s="9">
         <v>0.59635609999999994</v>
       </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A27" t="s">
+      <c r="P26" s="24">
+        <f t="shared" si="2"/>
+        <v>3.6514600000000002</v>
+      </c>
+    </row>
+    <row r="27" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A27" s="23" t="s">
         <v>27</v>
       </c>
       <c r="B27" s="7">
@@ -2033,9 +2083,13 @@
       <c r="N27" s="9">
         <v>0.44231540000000003</v>
       </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A28" t="s">
+      <c r="P27" s="24">
+        <f t="shared" si="2"/>
+        <v>-1.9185600000000012</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A28" s="23" t="s">
         <v>28</v>
       </c>
       <c r="B28" s="7">
@@ -2078,9 +2132,13 @@
       <c r="N28" s="9">
         <v>0.37441639999999998</v>
       </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
-      <c r="A29" t="s">
+      <c r="P28" s="24">
+        <f t="shared" si="2"/>
+        <v>1.6092500000000012</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="A29" s="23" t="s">
         <v>29</v>
       </c>
       <c r="B29" s="8">
@@ -2095,8 +2153,12 @@
       <c r="E29" s="8">
         <v>7409.2820000000002</v>
       </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="P29" s="24">
+        <f t="shared" si="2"/>
+        <v>12813.329999999998</v>
+      </c>
+    </row>
+    <row r="30" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>30</v>
       </c>
@@ -2188,21 +2250,21 @@
       <c r="C2" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="E2" s="21"/>
+      <c r="E2" s="22"/>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A3" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="22" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A4" s="16"/>
@@ -2402,13 +2464,13 @@
       <c r="H17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A18" t="s">
+      <c r="A18" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="29" t="s">
         <v>82</v>
       </c>
-      <c r="C18" s="14" t="s">
+      <c r="C18" s="29" t="s">
         <v>83</v>
       </c>
       <c r="E18" s="14" t="s">
@@ -2504,13 +2566,13 @@
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A26" t="s">
+      <c r="A26" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="B26" s="14" t="s">
+      <c r="B26" s="29" t="s">
         <v>105</v>
       </c>
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="29" t="s">
         <v>106</v>
       </c>
       <c r="E26" s="14" t="s">
@@ -2554,10 +2616,10 @@
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A30" t="s">
+      <c r="A30" s="23" t="s">
         <v>27</v>
       </c>
-      <c r="B30" s="14" t="s">
+      <c r="B30" s="29" t="s">
         <v>116</v>
       </c>
       <c r="C30" s="14" t="s">
@@ -2579,10 +2641,10 @@
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A32" t="s">
+      <c r="A32" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B32" s="29" t="s">
         <v>122</v>
       </c>
       <c r="C32" s="14" t="s">
